--- a/time_tracking.xlsx
+++ b/time_tracking.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxim/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxim/UCLL/Jaar 3/Sem 2/Research &amp; Expertise Project Digital Solutions/Interactive-3D-Force-Directed-Graph-Visualization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0624401D-3AF1-A145-A047-7419C6D54715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C3EB3C-A608-D241-8093-F3C4E0941749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="56">
   <si>
     <t>Date</t>
   </si>
@@ -185,12 +185,6 @@
     <t>cleanup/fix: duplicate function declarations, inconsistent variable names, CSS</t>
   </si>
   <si>
-    <t>TOTAL HOURS</t>
-  </si>
-  <si>
-    <t>Kick off &amp; planning</t>
-  </si>
-  <si>
     <t>Research</t>
   </si>
   <si>
@@ -198,6 +192,15 @@
   </si>
   <si>
     <t>feat: Excel -&gt; CouchDB import script + inspect tool; added xlsx + minimist deps</t>
+  </si>
+  <si>
+    <t>totaal:</t>
+  </si>
+  <si>
+    <t>Kick off / `planning</t>
+  </si>
+  <si>
+    <t>Refactor: improved structure to better explore the code for grading</t>
   </si>
 </sst>
 </file>
@@ -205,7 +208,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="d/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="d/mm/yyyy;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -214,13 +217,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -237,6 +233,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -357,58 +359,67 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -722,586 +733,624 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8">
+        <v>46136</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9">
+        <v>46137</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="8">
+        <v>46139</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="9">
+        <v>46141</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="8">
+        <v>46142</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="9">
+        <v>46146</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="8">
+        <v>46147</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="9">
+        <v>46148</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="8">
+        <v>46149</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
-    </row>
-    <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12">
-        <v>46136</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="9">
+        <v>46155</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="8">
+        <v>46156</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="9">
+        <v>46157</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="10">
+        <v>46160</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="9">
+        <v>46161</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="8">
+        <v>46162</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="6">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="9">
+        <v>46163</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="9">
+        <v>46169</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="3">
         <v>7</v>
       </c>
-      <c r="E3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="13">
-        <v>46137</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="8">
+        <v>46170</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="9">
+        <v>46171</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
+        <v>46172</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="9">
+        <v>46174</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46176</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
+        <v>46179</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46180</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
+        <v>46181</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12">
-        <v>46139</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="34" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
+        <v>46183</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D34" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E34" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12">
-        <v>46140</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="35" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46183</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="13">
-        <v>46141</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12">
-        <v>46142</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="C35" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46187</v>
+      </c>
+      <c r="B36" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="C36" s="18">
+        <v>0.4375</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="20">
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="13">
-        <v>46146</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="4">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12">
-        <v>46147</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13">
-        <v>46148</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="12">
-        <v>46149</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="19"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="20"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="20"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="19"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="20"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
-    </row>
-    <row r="15" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12">
-        <v>46154</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="13">
-        <v>46155</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="4">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12">
-        <v>46156</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="2">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13">
-        <v>46157</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14">
-        <v>46160</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13">
-        <v>46161</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12">
-        <v>46162</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="10">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="13">
-        <v>46163</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12">
-        <v>46168</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="13">
-        <v>46169</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12">
-        <v>46170</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="13">
-        <v>46171</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12">
-        <v>46172</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="10">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="13">
-        <v>46174</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12">
-        <v>46176</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="2">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="13">
-        <v>46179</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="4">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12">
-        <v>46180</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="13">
-        <v>46181</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="12">
-        <v>46182</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="13">
-        <v>46183</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E34" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="14">
-        <v>46183</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="10">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="6">
-        <f>E3+E4+E5+E7+E8+E9+E10+E11+E12+E13+E15+E16+E17+E18+E19+E20+E21+E22+E23+E24+E25+E26+E27+E28+E29+E30+E31+E32+E33+E34+E35</f>
-        <v>86</v>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="5">
+        <f>SUM(E3:E5)+SUM(E7:E13)+SUM(E15:E39)</f>
+        <v>87.5</v>
       </c>
     </row>
   </sheetData>

--- a/time_tracking.xlsx
+++ b/time_tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxim/UCLL/Jaar 3/Sem 2/Research &amp; Expertise Project Digital Solutions/Interactive-3D-Force-Directed-Graph-Visualization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C3EB3C-A608-D241-8093-F3C4E0941749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C95256-516B-EF44-AAEA-FC0A23241900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,89 +33,29 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>End</t>
-  </si>
-  <si>
     <t>Task</t>
   </si>
   <si>
     <t>Hours</t>
   </si>
   <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
     <t>Initial commit: repository setup, branching strategy</t>
   </si>
   <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
     <t>Reading assignment brief, understanding project requirements and scope</t>
   </si>
   <si>
-    <t>09:00</t>
-  </si>
-  <si>
     <t>Project scaffold: Express server, client folder, config files, README</t>
   </si>
   <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>Research: 3d-force-graph library — API, options, Three.js integration</t>
-  </si>
-  <si>
-    <t>Research: CouchDB concepts — document model, HTTP API, Fauxton UI</t>
-  </si>
-  <si>
-    <t>Research: CORDIS Horizon data — inspecting Excel files, understanding schema</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>CouchDB installation, admin user creation, CORS configuration (local.ini)</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>Research: D3 force simulation — charge, link strength, forceCollide</t>
-  </si>
-  <si>
-    <t>Designing CouchDB document schema: type field, _id conventions, link model</t>
-  </si>
-  <si>
-    <t>Research: Node.js async/await patterns, Express 5 routing, fetch API</t>
-  </si>
-  <si>
     <t>CouchDB import script design, couchdb-setup.md documentation (c2e96dd)</t>
   </si>
   <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
     <t>Testing import script: dry run, debugging field mappings, running full import</t>
   </si>
   <si>
@@ -128,15 +68,9 @@
     <t>Testing live graph with full dataset; tuning charge, node size, colours</t>
   </si>
   <si>
-    <t>13:30</t>
-  </si>
-  <si>
     <t>feat(ui): preview/full toggle, text filter, sampling slider, link weights</t>
   </si>
   <si>
-    <t>16:00</t>
-  </si>
-  <si>
     <t>Testing filter/preview features; debugging sampler edge cases</t>
   </si>
   <si>
@@ -161,18 +95,12 @@
     <t>Designing node detail panel: field layout per type, CSS variables, chip styles</t>
   </si>
   <si>
-    <t>12:30</t>
-  </si>
-  <si>
     <t>fix(graph loading): reusable fetch functions; silent CouchDB failure root-cause</t>
   </si>
   <si>
     <t>Debugging fetch refactor; scoping node interaction implementation</t>
   </si>
   <si>
-    <t>17:30</t>
-  </si>
-  <si>
     <t>fix(fetching) + feat(node interaction): single fetch, panel, highlights, tooltips</t>
   </si>
   <si>
@@ -201,6 +129,33 @@
   </si>
   <si>
     <t>Refactor: improved structure to better explore the code for grading</t>
+  </si>
+  <si>
+    <t>Research: 3d-force-graph library</t>
+  </si>
+  <si>
+    <t>Research: CouchDB</t>
+  </si>
+  <si>
+    <t>Research: CORDIS Horizon dataset</t>
+  </si>
+  <si>
+    <t>Fix(ui): improved the controls panel</t>
+  </si>
+  <si>
+    <t>CouchDB installation, admin user creation, CORS config</t>
+  </si>
+  <si>
+    <t>Research: D3 force simulation</t>
+  </si>
+  <si>
+    <t>CouchDB document schema</t>
+  </si>
+  <si>
+    <t>Node.js async/await patterns, Express 5 routing, fetch API</t>
+  </si>
+  <si>
+    <t>Styling improvement for visibility, glowing fix + GLTF</t>
   </si>
 </sst>
 </file>
@@ -359,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -391,34 +346,28 @@
     <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -723,643 +672,436 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="66.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="2" max="2" width="66.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="15"/>
+    </row>
+    <row r="2" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="14"/>
       <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16"/>
-    </row>
-    <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>46136</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>46137</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>46139</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="15"/>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="14"/>
       <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="16"/>
-    </row>
-    <row r="7" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>46140</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>46141</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>46142</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>46146</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="B10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="3">
         <v>2.5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>46147</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>46148</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>46149</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="15"/>
+      <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="14"/>
       <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
-    </row>
-    <row r="15" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>46154</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="1">
+      <c r="B15" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <v>46155</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="3">
+        <v>28</v>
+      </c>
+      <c r="C16" s="3">
         <v>3.5</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>46156</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="1">
+      <c r="B17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="1">
         <v>2.5</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>46157</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="B18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10">
         <v>46160</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E19" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+      <c r="C19" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>46161</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>46162</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="6">
+      <c r="C21" s="6">
         <v>4.5</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>46163</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="B22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>46168</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>46169</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="3">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>46170</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="6">
+      <c r="B25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>46171</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="3">
+        <v>16</v>
+      </c>
+      <c r="C26" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>46172</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="6">
+      <c r="B27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="6">
         <v>1.5</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>46174</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="3">
+      <c r="C28" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>46176</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="1">
+      <c r="B29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="1">
         <v>1.5</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>46179</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="3">
+      <c r="B30" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="3">
         <v>2.5</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>46180</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="B31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>46181</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="3">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>46182</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="B33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>46183</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E34" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="C34" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46183</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="6">
+      <c r="B35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="6">
         <v>3.5</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46187</v>
       </c>
-      <c r="B36" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="C36" s="18">
-        <v>0.4375</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="20">
+      <c r="B36" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="12">
         <v>1.5</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="20"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="20"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="19"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="20"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="5">
-        <f>SUM(E3:E5)+SUM(E7:E13)+SUM(E15:E39)</f>
-        <v>87.5</v>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="18">
+        <v>46187</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="18">
+        <v>46187</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="12"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="5">
+        <f>SUM(C3:C5)+SUM(C7:C13)+SUM(C15:C39)</f>
+        <v>79.25</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A14:E14"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/time_tracking.xlsx
+++ b/time_tracking.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxim/UCLL/Jaar 3/Sem 2/Research &amp; Expertise Project Digital Solutions/Interactive-3D-Force-Directed-Graph-Visualization/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C95256-516B-EF44-AAEA-FC0A23241900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A1EA45-9664-2E4F-AE86-234621F6B032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="21460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Date</t>
   </si>
@@ -44,6 +44,9 @@
     <t>Hours</t>
   </si>
   <si>
+    <t>Kick off / `planning</t>
+  </si>
+  <si>
     <t>Initial commit: repository setup, branching strategy</t>
   </si>
   <si>
@@ -53,9 +56,39 @@
     <t>Project scaffold: Express server, client folder, config files, README</t>
   </si>
   <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>Research: 3d-force-graph library</t>
+  </si>
+  <si>
+    <t>Research: CouchDB</t>
+  </si>
+  <si>
+    <t>Research: CORDIS Horizon dataset</t>
+  </si>
+  <si>
+    <t>CouchDB installation, admin user creation, CORS config</t>
+  </si>
+  <si>
+    <t>Research: D3 force simulation</t>
+  </si>
+  <si>
+    <t>CouchDB document schema</t>
+  </si>
+  <si>
+    <t>Node.js async/await patterns, Express 5 routing, fetch API</t>
+  </si>
+  <si>
+    <t>Development</t>
+  </si>
+  <si>
     <t>CouchDB import script design, couchdb-setup.md documentation (c2e96dd)</t>
   </si>
   <si>
+    <t>feat: Excel -&gt; CouchDB import script + inspect tool; added xlsx + minimist deps</t>
+  </si>
+  <si>
     <t>Testing import script: dry run, debugging field mappings, running full import</t>
   </si>
   <si>
@@ -113,57 +146,28 @@
     <t>cleanup/fix: duplicate function declarations, inconsistent variable names, CSS</t>
   </si>
   <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>Development</t>
-  </si>
-  <si>
-    <t>feat: Excel -&gt; CouchDB import script + inspect tool; added xlsx + minimist deps</t>
+    <t>Refactor: improved structure to better explore the code for grading</t>
+  </si>
+  <si>
+    <t>Fix(ui): improved the controls panel</t>
+  </si>
+  <si>
+    <t>Styling improvement for visibility, glowing fix + GLTF</t>
   </si>
   <si>
     <t>totaal:</t>
   </si>
   <si>
-    <t>Kick off / `planning</t>
-  </si>
-  <si>
-    <t>Refactor: improved structure to better explore the code for grading</t>
-  </si>
-  <si>
-    <t>Research: 3d-force-graph library</t>
-  </si>
-  <si>
-    <t>Research: CouchDB</t>
-  </si>
-  <si>
-    <t>Research: CORDIS Horizon dataset</t>
-  </si>
-  <si>
-    <t>Fix(ui): improved the controls panel</t>
-  </si>
-  <si>
-    <t>CouchDB installation, admin user creation, CORS config</t>
-  </si>
-  <si>
-    <t>Research: D3 force simulation</t>
-  </si>
-  <si>
-    <t>CouchDB document schema</t>
-  </si>
-  <si>
-    <t>Node.js async/await patterns, Express 5 routing, fetch API</t>
-  </si>
-  <si>
-    <t>Styling improvement for visibility, glowing fix + GLTF</t>
+    <t>fix(modules): duplicate export, missing imports, GLTFLoader importmap, script load order</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="d/mm/yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -314,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -369,6 +373,12 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -672,7 +682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -693,7 +703,7 @@
     </row>
     <row r="2" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="15"/>
@@ -703,7 +713,7 @@
         <v>46136</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
@@ -714,7 +724,7 @@
         <v>46137</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3">
         <v>0.5</v>
@@ -725,7 +735,7 @@
         <v>46139</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
@@ -733,7 +743,7 @@
     </row>
     <row r="6" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="15"/>
@@ -743,7 +753,7 @@
         <v>46140</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1">
         <v>2.5</v>
@@ -754,7 +764,7 @@
         <v>46141</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3">
         <v>2</v>
@@ -765,7 +775,7 @@
         <v>46142</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C9" s="1">
         <v>0.75</v>
@@ -776,7 +786,7 @@
         <v>46146</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3">
         <v>2.5</v>
@@ -787,7 +797,7 @@
         <v>46147</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>2</v>
@@ -798,7 +808,7 @@
         <v>46148</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -809,7 +819,7 @@
         <v>46149</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1">
         <v>0.5</v>
@@ -817,7 +827,7 @@
     </row>
     <row r="14" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="15"/>
@@ -827,7 +837,7 @@
         <v>46154</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
@@ -838,7 +848,7 @@
         <v>46155</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3">
         <v>3.5</v>
@@ -849,7 +859,7 @@
         <v>46156</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C17" s="1">
         <v>2.5</v>
@@ -860,7 +870,7 @@
         <v>46157</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C18" s="3">
         <v>3</v>
@@ -871,7 +881,7 @@
         <v>46160</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C19" s="6">
         <v>3</v>
@@ -882,7 +892,7 @@
         <v>46161</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C20" s="3">
         <v>1.5</v>
@@ -893,7 +903,7 @@
         <v>46162</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C21" s="6">
         <v>4.5</v>
@@ -904,7 +914,7 @@
         <v>46163</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C22" s="3">
         <v>2</v>
@@ -915,7 +925,7 @@
         <v>46168</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
@@ -926,7 +936,7 @@
         <v>46169</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C24" s="3">
         <v>5.5</v>
@@ -937,7 +947,7 @@
         <v>46170</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C25" s="6">
         <v>4</v>
@@ -948,7 +958,7 @@
         <v>46171</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C26" s="3">
         <v>3</v>
@@ -959,7 +969,7 @@
         <v>46172</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C27" s="6">
         <v>1.5</v>
@@ -970,7 +980,7 @@
         <v>46174</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C28" s="3">
         <v>2</v>
@@ -981,7 +991,7 @@
         <v>46176</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C29" s="1">
         <v>1.5</v>
@@ -992,7 +1002,7 @@
         <v>46179</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C30" s="3">
         <v>2.5</v>
@@ -1003,7 +1013,7 @@
         <v>46180</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C31" s="1">
         <v>2</v>
@@ -1014,7 +1024,7 @@
         <v>46181</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C32" s="3">
         <v>4.5</v>
@@ -1025,7 +1035,7 @@
         <v>46182</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C33" s="1">
         <v>2</v>
@@ -1036,7 +1046,7 @@
         <v>46183</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C34" s="3">
         <v>2</v>
@@ -1047,7 +1057,7 @@
         <v>46183</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C35" s="6">
         <v>3.5</v>
@@ -1058,7 +1068,7 @@
         <v>46187</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C36" s="12">
         <v>1.5</v>
@@ -1069,7 +1079,7 @@
         <v>46187</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C37" s="12">
         <v>1</v>
@@ -1080,25 +1090,31 @@
         <v>46187</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C38" s="12">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="5">
+      <c r="A39" s="19">
+        <v>46188</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="17"/>
+      <c r="C42" s="5">
         <f>SUM(C3:C5)+SUM(C7:C13)+SUM(C15:C39)</f>
-        <v>79.25</v>
+        <v>81.25</v>
       </c>
     </row>
   </sheetData>
